--- a/out/Расходы-по-контрагентам-Август-2026.xlsx
+++ b/out/Расходы-по-контрагентам-Август-2026.xlsx
@@ -83,16 +83,17 @@
     <font>
       <b val="1"/>
       <color rgb="008A6A3C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008A6A3C"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001A1613"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <color rgb="00EFEAE2"/>
-      <sz val="8"/>
     </font>
   </fonts>
   <fills count="5">
@@ -166,21 +167,20 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
@@ -188,6 +188,7 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6616,20 +6617,20 @@
           <t>Сумма статьи — SUMIF по листу «Контрагенты». База для доли переключается в C4.</t>
         </is>
       </c>
-      <c r="C3" s="34">
-        <f>IF($C$4="суммы по контрагентам",Контрагенты!$C$125,Свод!$C$143)</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>Доля считается от:</t>
-        </is>
-      </c>
-      <c r="C4" s="35" t="inlineStr">
-        <is>
-          <t>расходов учредителей</t>
+          <t>Доля считается от суммы по контрагентам:</t>
+        </is>
+      </c>
+      <c r="C4" s="34">
+        <f>Контрагенты!$C$125</f>
+        <v/>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ручные поправки в базу не входят — они не разнесены по статьям</t>
         </is>
       </c>
     </row>
@@ -6661,14 +6662,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>МЕДИЦИНСКИЕ</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>Анализы</t>
         </is>
@@ -6682,8 +6683,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B8&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E8" s="38">
-        <f>IF($C$3=0,0,D8/$C$3)</f>
+      <c r="E8" s="37">
+        <f>IF($C$4=0,0,D8/$C$4)</f>
         <v/>
       </c>
       <c r="F8" s="29">
@@ -6692,7 +6693,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>Аренда Inmode</t>
         </is>
@@ -6706,8 +6707,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B9&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E9" s="38">
-        <f>IF($C$3=0,0,D9/$C$3)</f>
+      <c r="E9" s="37">
+        <f>IF($C$4=0,0,D9/$C$4)</f>
         <v/>
       </c>
       <c r="F9" s="29">
@@ -6716,7 +6717,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
@@ -6730,8 +6731,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B10&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E10" s="38">
-        <f>IF($C$3=0,0,D10/$C$3)</f>
+      <c r="E10" s="37">
+        <f>IF($C$4=0,0,D10/$C$4)</f>
         <v/>
       </c>
       <c r="F10" s="29">
@@ -6740,7 +6741,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>Бланки, мед.журналы, мед.книжки</t>
         </is>
@@ -6754,8 +6755,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B11&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E11" s="38">
-        <f>IF($C$3=0,0,D11/$C$3)</f>
+      <c r="E11" s="37">
+        <f>IF($C$4=0,0,D11/$C$4)</f>
         <v/>
       </c>
       <c r="F11" s="29">
@@ -6764,7 +6765,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Вывоз ТКО и мед отходов</t>
         </is>
@@ -6778,8 +6779,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B12&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E12" s="38">
-        <f>IF($C$3=0,0,D12/$C$3)</f>
+      <c r="E12" s="37">
+        <f>IF($C$4=0,0,D12/$C$4)</f>
         <v/>
       </c>
       <c r="F12" s="29">
@@ -6788,7 +6789,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -6802,8 +6803,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B13&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E13" s="38">
-        <f>IF($C$3=0,0,D13/$C$3)</f>
+      <c r="E13" s="37">
+        <f>IF($C$4=0,0,D13/$C$4)</f>
         <v/>
       </c>
       <c r="F13" s="29">
@@ -6812,7 +6813,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>ИП Завиркин А.В.</t>
         </is>
@@ -6826,8 +6827,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B14&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E14" s="38">
-        <f>IF($C$3=0,0,D14/$C$3)</f>
+      <c r="E14" s="37">
+        <f>IF($C$4=0,0,D14/$C$4)</f>
         <v/>
       </c>
       <c r="F14" s="29">
@@ -6836,7 +6837,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
@@ -6850,8 +6851,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B15&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E15" s="38">
-        <f>IF($C$3=0,0,D15/$C$3)</f>
+      <c r="E15" s="37">
+        <f>IF($C$4=0,0,D15/$C$4)</f>
         <v/>
       </c>
       <c r="F15" s="29">
@@ -6860,7 +6861,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
@@ -6874,8 +6875,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B16&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E16" s="38">
-        <f>IF($C$3=0,0,D16/$C$3)</f>
+      <c r="E16" s="37">
+        <f>IF($C$4=0,0,D16/$C$4)</f>
         <v/>
       </c>
       <c r="F16" s="29">
@@ -6884,7 +6885,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>Кровь</t>
         </is>
@@ -6898,8 +6899,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B17&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E17" s="38">
-        <f>IF($C$3=0,0,D17/$C$3)</f>
+      <c r="E17" s="37">
+        <f>IF($C$4=0,0,D17/$C$4)</f>
         <v/>
       </c>
       <c r="F17" s="29">
@@ -6908,7 +6909,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
@@ -6922,8 +6923,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B18&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E18" s="38">
-        <f>IF($C$3=0,0,D18/$C$3)</f>
+      <c r="E18" s="37">
+        <f>IF($C$4=0,0,D18/$C$4)</f>
         <v/>
       </c>
       <c r="F18" s="29">
@@ -6932,7 +6933,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Мед.инструмент</t>
         </is>
@@ -6946,8 +6947,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B19&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E19" s="38">
-        <f>IF($C$3=0,0,D19/$C$3)</f>
+      <c r="E19" s="37">
+        <f>IF($C$4=0,0,D19/$C$4)</f>
         <v/>
       </c>
       <c r="F19" s="29">
@@ -6956,7 +6957,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>Мед.мебель</t>
         </is>
@@ -6970,8 +6971,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B20&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E20" s="38">
-        <f>IF($C$3=0,0,D20/$C$3)</f>
+      <c r="E20" s="37">
+        <f>IF($C$4=0,0,D20/$C$4)</f>
         <v/>
       </c>
       <c r="F20" s="29">
@@ -6980,7 +6981,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -6994,8 +6995,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B21&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E21" s="38">
-        <f>IF($C$3=0,0,D21/$C$3)</f>
+      <c r="E21" s="37">
+        <f>IF($C$4=0,0,D21/$C$4)</f>
         <v/>
       </c>
       <c r="F21" s="29">
@@ -7004,7 +7005,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>Медоборудование</t>
         </is>
@@ -7018,8 +7019,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B22&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E22" s="38">
-        <f>IF($C$3=0,0,D22/$C$3)</f>
+      <c r="E22" s="37">
+        <f>IF($C$4=0,0,D22/$C$4)</f>
         <v/>
       </c>
       <c r="F22" s="29">
@@ -7028,7 +7029,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>Медоборудование 320588 и расходники 194940</t>
         </is>
@@ -7042,8 +7043,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B23&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E23" s="38">
-        <f>IF($C$3=0,0,D23/$C$3)</f>
+      <c r="E23" s="37">
+        <f>IF($C$4=0,0,D23/$C$4)</f>
         <v/>
       </c>
       <c r="F23" s="29">
@@ -7052,7 +7053,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>Наркотики</t>
         </is>
@@ -7066,8 +7067,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B24&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E24" s="38">
-        <f>IF($C$3=0,0,D24/$C$3)</f>
+      <c r="E24" s="37">
+        <f>IF($C$4=0,0,D24/$C$4)</f>
         <v/>
       </c>
       <c r="F24" s="29">
@@ -7076,7 +7077,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>Питание</t>
         </is>
@@ -7090,8 +7091,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B25&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E25" s="38">
-        <f>IF($C$3=0,0,D25/$C$3)</f>
+      <c r="E25" s="37">
+        <f>IF($C$4=0,0,D25/$C$4)</f>
         <v/>
       </c>
       <c r="F25" s="29">
@@ -7100,7 +7101,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -7114,8 +7115,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B26&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E26" s="38">
-        <f>IF($C$3=0,0,D26/$C$3)</f>
+      <c r="E26" s="37">
+        <f>IF($C$4=0,0,D26/$C$4)</f>
         <v/>
       </c>
       <c r="F26" s="29">
@@ -7124,7 +7125,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>Стиральный порошок</t>
         </is>
@@ -7138,8 +7139,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B27&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E27" s="38">
-        <f>IF($C$3=0,0,D27/$C$3)</f>
+      <c r="E27" s="37">
+        <f>IF($C$4=0,0,D27/$C$4)</f>
         <v/>
       </c>
       <c r="F27" s="29">
@@ -7148,7 +7149,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>Утилизация медотходов</t>
         </is>
@@ -7162,8 +7163,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B28&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E28" s="38">
-        <f>IF($C$3=0,0,D28/$C$3)</f>
+      <c r="E28" s="37">
+        <f>IF($C$4=0,0,D28/$C$4)</f>
         <v/>
       </c>
       <c r="F28" s="29">
@@ -7182,21 +7183,21 @@
         <f>SUM(D8:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="39">
-        <f>IF($C$3=0,0,D29/$C$3)</f>
+      <c r="E29" s="38">
+        <f>IF($C$4=0,0,D29/$C$4)</f>
         <v/>
       </c>
       <c r="F29" s="16" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="36" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>УПРАВЛЕНЧЕСКИЕ</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="37" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
@@ -7210,8 +7211,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B32&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E32" s="38">
-        <f>IF($C$3=0,0,D32/$C$3)</f>
+      <c r="E32" s="37">
+        <f>IF($C$4=0,0,D32/$C$4)</f>
         <v/>
       </c>
       <c r="F32" s="29">
@@ -7220,7 +7221,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="37" t="inlineStr">
+      <c r="B33" s="36" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр1</t>
         </is>
@@ -7234,8 +7235,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B33&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E33" s="38">
-        <f>IF($C$3=0,0,D33/$C$3)</f>
+      <c r="E33" s="37">
+        <f>IF($C$4=0,0,D33/$C$4)</f>
         <v/>
       </c>
       <c r="F33" s="29">
@@ -7244,7 +7245,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="37" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>Аренда кофемашины</t>
         </is>
@@ -7258,8 +7259,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B34&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E34" s="38">
-        <f>IF($C$3=0,0,D34/$C$3)</f>
+      <c r="E34" s="37">
+        <f>IF($C$4=0,0,D34/$C$4)</f>
         <v/>
       </c>
       <c r="F34" s="29">
@@ -7268,7 +7269,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="37" t="inlineStr">
+      <c r="B35" s="36" t="inlineStr">
         <is>
           <t>Битрикс 24</t>
         </is>
@@ -7282,8 +7283,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B35&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E35" s="38">
-        <f>IF($C$3=0,0,D35/$C$3)</f>
+      <c r="E35" s="37">
+        <f>IF($C$4=0,0,D35/$C$4)</f>
         <v/>
       </c>
       <c r="F35" s="29">
@@ -7292,7 +7293,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="37" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>Внедрение финансового учёта</t>
         </is>
@@ -7306,8 +7307,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B36&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E36" s="38">
-        <f>IF($C$3=0,0,D36/$C$3)</f>
+      <c r="E36" s="37">
+        <f>IF($C$4=0,0,D36/$C$4)</f>
         <v/>
       </c>
       <c r="F36" s="29">
@@ -7316,7 +7317,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="37" t="inlineStr">
+      <c r="B37" s="36" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
@@ -7330,8 +7331,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B37&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E37" s="38">
-        <f>IF($C$3=0,0,D37/$C$3)</f>
+      <c r="E37" s="37">
+        <f>IF($C$4=0,0,D37/$C$4)</f>
         <v/>
       </c>
       <c r="F37" s="29">
@@ -7340,7 +7341,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>Дизайн-услуги</t>
         </is>
@@ -7354,8 +7355,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B38&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E38" s="38">
-        <f>IF($C$3=0,0,D38/$C$3)</f>
+      <c r="E38" s="37">
+        <f>IF($C$4=0,0,D38/$C$4)</f>
         <v/>
       </c>
       <c r="F38" s="29">
@@ -7364,7 +7365,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
@@ -7378,8 +7379,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B39&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E39" s="38">
-        <f>IF($C$3=0,0,D39/$C$3)</f>
+      <c r="E39" s="37">
+        <f>IF($C$4=0,0,D39/$C$4)</f>
         <v/>
       </c>
       <c r="F39" s="29">
@@ -7388,7 +7389,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="37" t="inlineStr">
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>Интернет</t>
         </is>
@@ -7402,8 +7403,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B40&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E40" s="38">
-        <f>IF($C$3=0,0,D40/$C$3)</f>
+      <c r="E40" s="37">
+        <f>IF($C$4=0,0,D40/$C$4)</f>
         <v/>
       </c>
       <c r="F40" s="29">
@@ -7412,7 +7413,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B41" s="36" t="inlineStr">
         <is>
           <t>Канц и хоз расходы</t>
         </is>
@@ -7426,8 +7427,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B41&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E41" s="38">
-        <f>IF($C$3=0,0,D41/$C$3)</f>
+      <c r="E41" s="37">
+        <f>IF($C$4=0,0,D41/$C$4)</f>
         <v/>
       </c>
       <c r="F41" s="29">
@@ -7436,7 +7437,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="37" t="inlineStr">
+      <c r="B42" s="36" t="inlineStr">
         <is>
           <t>Консультационные услуги</t>
         </is>
@@ -7450,8 +7451,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B42&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E42" s="38">
-        <f>IF($C$3=0,0,D42/$C$3)</f>
+      <c r="E42" s="37">
+        <f>IF($C$4=0,0,D42/$C$4)</f>
         <v/>
       </c>
       <c r="F42" s="29">
@@ -7460,7 +7461,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B43" s="36" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -7474,8 +7475,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B43&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E43" s="38">
-        <f>IF($C$3=0,0,D43/$C$3)</f>
+      <c r="E43" s="37">
+        <f>IF($C$4=0,0,D43/$C$4)</f>
         <v/>
       </c>
       <c r="F43" s="29">
@@ -7484,7 +7485,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B44" s="36" t="inlineStr">
         <is>
           <t>Кофе</t>
         </is>
@@ -7498,8 +7499,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B44&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E44" s="38">
-        <f>IF($C$3=0,0,D44/$C$3)</f>
+      <c r="E44" s="37">
+        <f>IF($C$4=0,0,D44/$C$4)</f>
         <v/>
       </c>
       <c r="F44" s="29">
@@ -7508,7 +7509,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="37" t="inlineStr">
+      <c r="B45" s="36" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
@@ -7522,8 +7523,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B45&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E45" s="38">
-        <f>IF($C$3=0,0,D45/$C$3)</f>
+      <c r="E45" s="37">
+        <f>IF($C$4=0,0,D45/$C$4)</f>
         <v/>
       </c>
       <c r="F45" s="29">
@@ -7532,7 +7533,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="37" t="inlineStr">
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t>Маркетинговые услуги</t>
         </is>
@@ -7546,8 +7547,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B46&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E46" s="38">
-        <f>IF($C$3=0,0,D46/$C$3)</f>
+      <c r="E46" s="37">
+        <f>IF($C$4=0,0,D46/$C$4)</f>
         <v/>
       </c>
       <c r="F46" s="29">
@@ -7556,7 +7557,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="37" t="inlineStr">
+      <c r="B47" s="36" t="inlineStr">
         <is>
           <t>Мебель, инвентарь</t>
         </is>
@@ -7570,8 +7571,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B47&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E47" s="38">
-        <f>IF($C$3=0,0,D47/$C$3)</f>
+      <c r="E47" s="37">
+        <f>IF($C$4=0,0,D47/$C$4)</f>
         <v/>
       </c>
       <c r="F47" s="29">
@@ -7580,7 +7581,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="37" t="inlineStr">
+      <c r="B48" s="36" t="inlineStr">
         <is>
           <t>Обслуживание 1СПредприятие</t>
         </is>
@@ -7594,8 +7595,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B48&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E48" s="38">
-        <f>IF($C$3=0,0,D48/$C$3)</f>
+      <c r="E48" s="37">
+        <f>IF($C$4=0,0,D48/$C$4)</f>
         <v/>
       </c>
       <c r="F48" s="29">
@@ -7604,7 +7605,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="37" t="inlineStr">
+      <c r="B49" s="36" t="inlineStr">
         <is>
           <t>Обслуживание 1СУправление</t>
         </is>
@@ -7618,8 +7619,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B49&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E49" s="38">
-        <f>IF($C$3=0,0,D49/$C$3)</f>
+      <c r="E49" s="37">
+        <f>IF($C$4=0,0,D49/$C$4)</f>
         <v/>
       </c>
       <c r="F49" s="29">
@@ -7628,7 +7629,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="37" t="inlineStr">
+      <c r="B50" s="36" t="inlineStr">
         <is>
           <t>Обслуживание ККТ</t>
         </is>
@@ -7642,8 +7643,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B50&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E50" s="38">
-        <f>IF($C$3=0,0,D50/$C$3)</f>
+      <c r="E50" s="37">
+        <f>IF($C$4=0,0,D50/$C$4)</f>
         <v/>
       </c>
       <c r="F50" s="29">
@@ -7652,7 +7653,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="37" t="inlineStr">
+      <c r="B51" s="36" t="inlineStr">
         <is>
           <t>Обслуживание аквариума</t>
         </is>
@@ -7666,8 +7667,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B51&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E51" s="38">
-        <f>IF($C$3=0,0,D51/$C$3)</f>
+      <c r="E51" s="37">
+        <f>IF($C$4=0,0,D51/$C$4)</f>
         <v/>
       </c>
       <c r="F51" s="29">
@@ -7676,7 +7677,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="37" t="inlineStr">
+      <c r="B52" s="36" t="inlineStr">
         <is>
           <t>Обучение персонала</t>
         </is>
@@ -7690,8 +7691,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B52&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E52" s="38">
-        <f>IF($C$3=0,0,D52/$C$3)</f>
+      <c r="E52" s="37">
+        <f>IF($C$4=0,0,D52/$C$4)</f>
         <v/>
       </c>
       <c r="F52" s="29">
@@ -7700,7 +7701,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="37" t="inlineStr">
+      <c r="B53" s="36" t="inlineStr">
         <is>
           <t>Общехоз.расходы прочие</t>
         </is>
@@ -7714,8 +7715,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B53&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E53" s="38">
-        <f>IF($C$3=0,0,D53/$C$3)</f>
+      <c r="E53" s="37">
+        <f>IF($C$4=0,0,D53/$C$4)</f>
         <v/>
       </c>
       <c r="F53" s="29">
@@ -7724,7 +7725,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="37" t="inlineStr">
+      <c r="B54" s="36" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
@@ -7738,8 +7739,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B54&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E54" s="38">
-        <f>IF($C$3=0,0,D54/$C$3)</f>
+      <c r="E54" s="37">
+        <f>IF($C$4=0,0,D54/$C$4)</f>
         <v/>
       </c>
       <c r="F54" s="29">
@@ -7748,7 +7749,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="37" t="inlineStr">
+      <c r="B55" s="36" t="inlineStr">
         <is>
           <t>Оргтехника</t>
         </is>
@@ -7762,8 +7763,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B55&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E55" s="38">
-        <f>IF($C$3=0,0,D55/$C$3)</f>
+      <c r="E55" s="37">
+        <f>IF($C$4=0,0,D55/$C$4)</f>
         <v/>
       </c>
       <c r="F55" s="29">
@@ -7772,7 +7773,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="37" t="inlineStr">
+      <c r="B56" s="36" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
@@ -7786,8 +7787,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B56&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E56" s="38">
-        <f>IF($C$3=0,0,D56/$C$3)</f>
+      <c r="E56" s="37">
+        <f>IF($C$4=0,0,D56/$C$4)</f>
         <v/>
       </c>
       <c r="F56" s="29">
@@ -7796,7 +7797,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="37" t="inlineStr">
+      <c r="B57" s="36" t="inlineStr">
         <is>
           <t>ПО и IT-сервисы</t>
         </is>
@@ -7810,8 +7811,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B57&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E57" s="38">
-        <f>IF($C$3=0,0,D57/$C$3)</f>
+      <c r="E57" s="37">
+        <f>IF($C$4=0,0,D57/$C$4)</f>
         <v/>
       </c>
       <c r="F57" s="29">
@@ -7820,7 +7821,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="37" t="inlineStr">
+      <c r="B58" s="36" t="inlineStr">
         <is>
           <t>Подбор персонала</t>
         </is>
@@ -7834,8 +7835,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B58&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E58" s="38">
-        <f>IF($C$3=0,0,D58/$C$3)</f>
+      <c r="E58" s="37">
+        <f>IF($C$4=0,0,D58/$C$4)</f>
         <v/>
       </c>
       <c r="F58" s="29">
@@ -7844,7 +7845,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="37" t="inlineStr">
+      <c r="B59" s="36" t="inlineStr">
         <is>
           <t>ПроДокторов</t>
         </is>
@@ -7858,8 +7859,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B59&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E59" s="38">
-        <f>IF($C$3=0,0,D59/$C$3)</f>
+      <c r="E59" s="37">
+        <f>IF($C$4=0,0,D59/$C$4)</f>
         <v/>
       </c>
       <c r="F59" s="29">
@@ -7868,7 +7869,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="37" t="inlineStr">
+      <c r="B60" s="36" t="inlineStr">
         <is>
           <t>Программное обнспечение</t>
         </is>
@@ -7882,8 +7883,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B60&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E60" s="38">
-        <f>IF($C$3=0,0,D60/$C$3)</f>
+      <c r="E60" s="37">
+        <f>IF($C$4=0,0,D60/$C$4)</f>
         <v/>
       </c>
       <c r="F60" s="29">
@@ -7892,7 +7893,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="37" t="inlineStr">
+      <c r="B61" s="36" t="inlineStr">
         <is>
           <t>Расходник</t>
         </is>
@@ -7906,8 +7907,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B61&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E61" s="38">
-        <f>IF($C$3=0,0,D61/$C$3)</f>
+      <c r="E61" s="37">
+        <f>IF($C$4=0,0,D61/$C$4)</f>
         <v/>
       </c>
       <c r="F61" s="29">
@@ -7916,7 +7917,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="37" t="inlineStr">
+      <c r="B62" s="36" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
@@ -7930,8 +7931,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B62&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E62" s="38">
-        <f>IF($C$3=0,0,D62/$C$3)</f>
+      <c r="E62" s="37">
+        <f>IF($C$4=0,0,D62/$C$4)</f>
         <v/>
       </c>
       <c r="F62" s="29">
@@ -7940,7 +7941,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="37" t="inlineStr">
+      <c r="B63" s="36" t="inlineStr">
         <is>
           <t>Ремонт</t>
         </is>
@@ -7954,8 +7955,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B63&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E63" s="38">
-        <f>IF($C$3=0,0,D63/$C$3)</f>
+      <c r="E63" s="37">
+        <f>IF($C$4=0,0,D63/$C$4)</f>
         <v/>
       </c>
       <c r="F63" s="29">
@@ -7964,7 +7965,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="37" t="inlineStr">
+      <c r="B64" s="36" t="inlineStr">
         <is>
           <t>Ремонт Самокатная 1 стр.12</t>
         </is>
@@ -7978,8 +7979,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B64&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E64" s="38">
-        <f>IF($C$3=0,0,D64/$C$3)</f>
+      <c r="E64" s="37">
+        <f>IF($C$4=0,0,D64/$C$4)</f>
         <v/>
       </c>
       <c r="F64" s="29">
@@ -7988,7 +7989,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="37" t="inlineStr">
+      <c r="B65" s="36" t="inlineStr">
         <is>
           <t>Ремонт керамогранит</t>
         </is>
@@ -8002,8 +8003,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B65&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E65" s="38">
-        <f>IF($C$3=0,0,D65/$C$3)</f>
+      <c r="E65" s="37">
+        <f>IF($C$4=0,0,D65/$C$4)</f>
         <v/>
       </c>
       <c r="F65" s="29">
@@ -8012,7 +8013,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="37" t="inlineStr">
+      <c r="B66" s="36" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
@@ -8026,8 +8027,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B66&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E66" s="38">
-        <f>IF($C$3=0,0,D66/$C$3)</f>
+      <c r="E66" s="37">
+        <f>IF($C$4=0,0,D66/$C$4)</f>
         <v/>
       </c>
       <c r="F66" s="29">
@@ -8036,7 +8037,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="37" t="inlineStr">
+      <c r="B67" s="36" t="inlineStr">
         <is>
           <t>Светильники и оборудование</t>
         </is>
@@ -8050,8 +8051,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B67&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E67" s="38">
-        <f>IF($C$3=0,0,D67/$C$3)</f>
+      <c r="E67" s="37">
+        <f>IF($C$4=0,0,D67/$C$4)</f>
         <v/>
       </c>
       <c r="F67" s="29">
@@ -8060,7 +8061,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="37" t="inlineStr">
+      <c r="B68" s="36" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -8074,8 +8075,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B68&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E68" s="38">
-        <f>IF($C$3=0,0,D68/$C$3)</f>
+      <c r="E68" s="37">
+        <f>IF($C$4=0,0,D68/$C$4)</f>
         <v/>
       </c>
       <c r="F68" s="29">
@@ -8084,7 +8085,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="37" t="inlineStr">
+      <c r="B69" s="36" t="inlineStr">
         <is>
           <t>Сервис речевой аналитики</t>
         </is>
@@ -8098,8 +8099,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B69&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E69" s="38">
-        <f>IF($C$3=0,0,D69/$C$3)</f>
+      <c r="E69" s="37">
+        <f>IF($C$4=0,0,D69/$C$4)</f>
         <v/>
       </c>
       <c r="F69" s="29">
@@ -8108,7 +8109,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="37" t="inlineStr">
+      <c r="B70" s="36" t="inlineStr">
         <is>
           <t>Складской учет</t>
         </is>
@@ -8122,8 +8123,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B70&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E70" s="38">
-        <f>IF($C$3=0,0,D70/$C$3)</f>
+      <c r="E70" s="37">
+        <f>IF($C$4=0,0,D70/$C$4)</f>
         <v/>
       </c>
       <c r="F70" s="29">
@@ -8132,7 +8133,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="37" t="inlineStr">
+      <c r="B71" s="36" t="inlineStr">
         <is>
           <t>Средства гигиены</t>
         </is>
@@ -8146,8 +8147,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B71&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E71" s="38">
-        <f>IF($C$3=0,0,D71/$C$3)</f>
+      <c r="E71" s="37">
+        <f>IF($C$4=0,0,D71/$C$4)</f>
         <v/>
       </c>
       <c r="F71" s="29">
@@ -8156,7 +8157,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="37" t="inlineStr">
+      <c r="B72" s="36" t="inlineStr">
         <is>
           <t>ТО СКУД, пожарной сигнализации</t>
         </is>
@@ -8170,8 +8171,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B72&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E72" s="38">
-        <f>IF($C$3=0,0,D72/$C$3)</f>
+      <c r="E72" s="37">
+        <f>IF($C$4=0,0,D72/$C$4)</f>
         <v/>
       </c>
       <c r="F72" s="29">
@@ -8180,7 +8181,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="37" t="inlineStr">
+      <c r="B73" s="36" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
@@ -8194,8 +8195,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B73&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E73" s="38">
-        <f>IF($C$3=0,0,D73/$C$3)</f>
+      <c r="E73" s="37">
+        <f>IF($C$4=0,0,D73/$C$4)</f>
         <v/>
       </c>
       <c r="F73" s="29">
@@ -8204,7 +8205,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="37" t="inlineStr">
+      <c r="B74" s="36" t="inlineStr">
         <is>
           <t>Техподдержка ККТ</t>
         </is>
@@ -8218,8 +8219,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B74&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E74" s="38">
-        <f>IF($C$3=0,0,D74/$C$3)</f>
+      <c r="E74" s="37">
+        <f>IF($C$4=0,0,D74/$C$4)</f>
         <v/>
       </c>
       <c r="F74" s="29">
@@ -8228,7 +8229,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="37" t="inlineStr">
+      <c r="B75" s="36" t="inlineStr">
         <is>
           <t>Урегулирование досудебного спора</t>
         </is>
@@ -8242,8 +8243,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B75&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E75" s="38">
-        <f>IF($C$3=0,0,D75/$C$3)</f>
+      <c r="E75" s="37">
+        <f>IF($C$4=0,0,D75/$C$4)</f>
         <v/>
       </c>
       <c r="F75" s="29">
@@ -8252,7 +8253,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="37" t="inlineStr">
+      <c r="B76" s="36" t="inlineStr">
         <is>
           <t>Услуги инженера</t>
         </is>
@@ -8266,8 +8267,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B76&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E76" s="38">
-        <f>IF($C$3=0,0,D76/$C$3)</f>
+      <c r="E76" s="37">
+        <f>IF($C$4=0,0,D76/$C$4)</f>
         <v/>
       </c>
       <c r="F76" s="29">
@@ -8276,7 +8277,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="37" t="inlineStr">
+      <c r="B77" s="36" t="inlineStr">
         <is>
           <t>Услуги юриста</t>
         </is>
@@ -8290,8 +8291,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B77&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E77" s="38">
-        <f>IF($C$3=0,0,D77/$C$3)</f>
+      <c r="E77" s="37">
+        <f>IF($C$4=0,0,D77/$C$4)</f>
         <v/>
       </c>
       <c r="F77" s="29">
@@ -8300,7 +8301,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="37" t="inlineStr">
+      <c r="B78" s="36" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
@@ -8314,8 +8315,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B78&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E78" s="38">
-        <f>IF($C$3=0,0,D78/$C$3)</f>
+      <c r="E78" s="37">
+        <f>IF($C$4=0,0,D78/$C$4)</f>
         <v/>
       </c>
       <c r="F78" s="29">
@@ -8324,7 +8325,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="37" t="inlineStr">
+      <c r="B79" s="36" t="inlineStr">
         <is>
           <t>Хоз расходы</t>
         </is>
@@ -8338,8 +8339,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B79&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E79" s="38">
-        <f>IF($C$3=0,0,D79/$C$3)</f>
+      <c r="E79" s="37">
+        <f>IF($C$4=0,0,D79/$C$4)</f>
         <v/>
       </c>
       <c r="F79" s="29">
@@ -8348,7 +8349,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="37" t="inlineStr">
+      <c r="B80" s="36" t="inlineStr">
         <is>
           <t>Цветы</t>
         </is>
@@ -8362,8 +8363,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B80&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E80" s="38">
-        <f>IF($C$3=0,0,D80/$C$3)</f>
+      <c r="E80" s="37">
+        <f>IF($C$4=0,0,D80/$C$4)</f>
         <v/>
       </c>
       <c r="F80" s="29">
@@ -8372,7 +8373,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="37" t="inlineStr">
+      <c r="B81" s="36" t="inlineStr">
         <is>
           <t>Электрооборудование</t>
         </is>
@@ -8386,8 +8387,8 @@
         <f>SUMIF(Контрагенты!$D$6:$D$124,B81&amp;"",Контрагенты!$C$6:$C$124)</f>
         <v/>
       </c>
-      <c r="E81" s="38">
-        <f>IF($C$3=0,0,D81/$C$3)</f>
+      <c r="E81" s="37">
+        <f>IF($C$4=0,0,D81/$C$4)</f>
         <v/>
       </c>
       <c r="F81" s="29">
@@ -8406,8 +8407,8 @@
         <f>SUM(D32:D81)</f>
         <v/>
       </c>
-      <c r="E82" s="39">
-        <f>IF($C$3=0,0,D82/$C$3)</f>
+      <c r="E82" s="38">
+        <f>IF($C$4=0,0,D82/$C$4)</f>
         <v/>
       </c>
       <c r="F82" s="16" t="n"/>
@@ -8418,22 +8419,21 @@
           <t>ВСЕГО ПО СТАТЬЯМ</t>
         </is>
       </c>
-      <c r="D84" s="40">
+      <c r="D84" s="39">
         <f>D29+D82</f>
         <v/>
       </c>
+      <c r="E84" s="40">
+        <f>IF($C$4=0,0,D84/$C$4)</f>
+        <v/>
+      </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>должно совпасть с суммой по контрагентам</t>
+          <t>сходится с суммой по контрагентам, доля 100,0 %</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"расходов учредителей,суммы по контрагентам"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>